--- a/Result/profitability/8021.xlsx
+++ b/Result/profitability/8021.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6925</v>
+        <v>0.8925000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>31.73875</v>
+        <v>33.50625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.73375</v>
+        <v>0.95125</v>
       </c>
       <c r="N3" t="n">
-        <v>33.0075</v>
+        <v>34.8375</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.86</v>
       </c>
       <c r="M4" t="n">
-        <v>0.79875</v>
+        <v>1.01375</v>
       </c>
       <c r="N4" t="n">
-        <v>33.84375</v>
+        <v>35.84</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.11</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7675000000000001</v>
+        <v>0.95875</v>
       </c>
       <c r="N5" t="n">
-        <v>33.37125</v>
+        <v>34.91375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0.72375</v>
+        <v>0.8875000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>32.29125</v>
+        <v>33.59875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.34</v>
       </c>
       <c r="M7" t="n">
-        <v>0.67</v>
+        <v>0.7975</v>
       </c>
       <c r="N7" t="n">
-        <v>31.9575</v>
+        <v>32.825</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.77</v>
       </c>
       <c r="M8" t="n">
-        <v>0.63375</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>31.59375</v>
+        <v>32.2425</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8021</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1826</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1063</v>
+      </c>
+      <c r="E75" t="n">
+        <v>763</v>
+      </c>
+      <c r="F75" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="G75" t="n">
+        <v>513</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>28.08%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>518</v>
+      </c>
+      <c r="K75" t="n">
+        <v>302</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8512500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.9100000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7777777777777779</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.189999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1418420333424433</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.781818181818182</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4191576086956521</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
